--- a/diseases/d037/1980-1984.xlsx
+++ b/diseases/d037/1980-1984.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>5</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>1</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>1</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>2</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>1</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>3</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>5</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>4</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>1</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>2</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>5</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>1</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>7</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>6</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>5</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>3</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>3</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9804,9 +9735,6 @@
       <c r="O48" t="n">
         <v>3</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10197,9 +10125,6 @@
       <c r="O50" t="n">
         <v>1</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10590,9 +10515,6 @@
       <c r="O52" t="n">
         <v>1</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10983,9 +10905,6 @@
       <c r="O54" t="n">
         <v>2</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11376,9 +11295,6 @@
       <c r="O56" t="n">
         <v>5</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11769,9 +11685,6 @@
       <c r="O58" t="n">
         <v>1</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12162,9 +12075,6 @@
       <c r="O60" t="n">
         <v>2</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12555,9 +12465,6 @@
       <c r="O62" t="n">
         <v>6</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12948,9 +12855,6 @@
       <c r="O64" t="n">
         <v>3</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13341,9 +13245,6 @@
       <c r="O66" t="n">
         <v>6</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13734,9 +13635,6 @@
       <c r="O68" t="n">
         <v>5</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14127,9 +14025,6 @@
       <c r="O70" t="n">
         <v>1</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14520,9 +14415,6 @@
       <c r="O72" t="n">
         <v>2</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="S72" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14913,9 +14805,6 @@
       <c r="O74" t="n">
         <v>1</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="S74" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15306,9 +15195,6 @@
       <c r="O76" t="n">
         <v>6</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="S76" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15699,9 +15585,6 @@
       <c r="O78" t="n">
         <v>4</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="S78" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16092,9 +15975,6 @@
       <c r="O80" t="n">
         <v>7</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16485,9 +16365,6 @@
       <c r="O82" t="n">
         <v>2</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="S82" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16878,9 +16755,6 @@
       <c r="O84" t="n">
         <v>5</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="S84" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17271,9 +17145,6 @@
       <c r="O86" t="n">
         <v>12</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="S86" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17664,9 +17535,6 @@
       <c r="O88" t="n">
         <v>9</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18057,9 +17925,6 @@
       <c r="O90" t="n">
         <v>7</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="S90" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18450,9 +18315,6 @@
       <c r="O92" t="n">
         <v>8</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18843,9 +18705,6 @@
       <c r="O94" t="n">
         <v>6</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="S94" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19236,9 +19095,6 @@
       <c r="O96" t="n">
         <v>2</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="S96" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19629,9 +19485,6 @@
       <c r="O98" t="n">
         <v>4</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="S98" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20022,9 +19875,6 @@
       <c r="O100" t="n">
         <v>5</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="S100" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20415,9 +20265,6 @@
       <c r="O102" t="n">
         <v>2</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="S102" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20808,9 +20655,6 @@
       <c r="O104" t="n">
         <v>3</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="S104" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21201,9 +21045,6 @@
       <c r="O106" t="n">
         <v>5</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="S106" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21594,9 +21435,6 @@
       <c r="O108" t="n">
         <v>9</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="S108" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21987,9 +21825,6 @@
       <c r="O110" t="n">
         <v>9</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="S110" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22380,9 +22215,6 @@
       <c r="O112" t="n">
         <v>11</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="S112" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22773,9 +22605,6 @@
       <c r="O114" t="n">
         <v>5</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="S114" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23166,9 +22995,6 @@
       <c r="O116" t="n">
         <v>5</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="S116" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23559,9 +23385,6 @@
       <c r="O118" t="n">
         <v>7</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="S118" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23951,9 +23774,6 @@
       </c>
       <c r="O120" t="n">
         <v>3</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>0</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>

--- a/diseases/d037/1980-1984.xlsx
+++ b/diseases/d037/1980-1984.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -795,17 +795,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS2" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -1021,7 +1026,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1029,17 +1034,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS3" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1177,7 +1187,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1185,17 +1195,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS4" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1411,7 +1426,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1419,17 +1434,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1567,7 +1587,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1575,17 +1595,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1801,7 +1826,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1809,17 +1834,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -1957,7 +1987,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -1965,17 +1995,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2191,7 +2226,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2199,17 +2234,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2347,7 +2387,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2355,17 +2395,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2581,7 +2626,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2589,17 +2634,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2737,7 +2787,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -2745,17 +2795,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -2971,7 +3026,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -2979,17 +3034,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS13" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -3127,7 +3187,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -3135,17 +3195,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS14" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -3361,7 +3426,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -3369,17 +3434,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS15" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -3517,7 +3587,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -3525,17 +3595,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS16" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -3751,7 +3826,7 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -3759,17 +3834,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS17" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -3907,7 +3987,7 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -3915,17 +3995,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS18" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -4141,7 +4226,7 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
@@ -4149,17 +4234,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS19" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -4297,7 +4387,7 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
@@ -4305,17 +4395,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS20" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -4531,7 +4626,7 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
@@ -4539,17 +4634,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS21" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -4687,7 +4787,7 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
@@ -4695,17 +4795,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS22" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -4921,7 +5026,7 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
@@ -4929,17 +5034,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS23" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -5077,7 +5187,7 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
@@ -5085,17 +5195,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS24" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -5311,7 +5426,7 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
@@ -5319,17 +5434,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS25" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -5467,7 +5587,7 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
@@ -5475,17 +5595,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS26" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -5701,7 +5826,7 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
@@ -5709,17 +5834,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS27" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -5857,7 +5987,7 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
@@ -5865,17 +5995,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS28" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -6091,7 +6226,7 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
@@ -6099,17 +6234,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS29" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -6247,7 +6387,7 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
@@ -6255,17 +6395,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS30" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -6481,7 +6626,7 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
@@ -6489,17 +6634,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS31" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -6637,7 +6787,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
@@ -6645,17 +6795,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS32" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -6871,7 +7026,7 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
@@ -6879,17 +7034,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS33" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -7027,7 +7187,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
@@ -7035,17 +7195,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS34" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -7261,7 +7426,7 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
@@ -7269,17 +7434,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS35" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -7417,7 +7587,7 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
@@ -7425,17 +7595,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS36" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -7651,7 +7826,7 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
@@ -7659,17 +7834,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS37" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -7807,7 +7987,7 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
@@ -7815,17 +7995,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS38" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -8041,7 +8226,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
@@ -8049,17 +8234,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS39" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -8197,7 +8387,7 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ40" t="inlineStr">
@@ -8205,17 +8395,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS40" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -8431,7 +8626,7 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
@@ -8439,17 +8634,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS41" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -8587,7 +8787,7 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
@@ -8595,17 +8795,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS42" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -8821,7 +9026,7 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
@@ -8829,17 +9034,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS43" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -8977,7 +9187,7 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
@@ -8985,17 +9195,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS44" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -9211,7 +9426,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
@@ -9219,17 +9434,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS45" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -9367,7 +9587,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
@@ -9375,17 +9595,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS46" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -9601,7 +9826,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
@@ -9609,17 +9834,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS47" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -9757,7 +9987,7 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ48" t="inlineStr">
@@ -9765,17 +9995,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS48" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -9991,7 +10226,7 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
@@ -9999,17 +10234,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS49" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -10147,7 +10387,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
@@ -10155,17 +10395,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS50" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -10381,7 +10626,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
@@ -10389,17 +10634,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS51" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -10537,7 +10787,7 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
@@ -10545,17 +10795,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS52" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -10771,7 +11026,7 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
@@ -10779,17 +11034,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS53" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -10927,7 +11187,7 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ54" t="inlineStr">
@@ -10935,17 +11195,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS54" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
@@ -11161,7 +11426,7 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
@@ -11169,17 +11434,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS55" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -11317,7 +11587,7 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
@@ -11325,17 +11595,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS56" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -11551,7 +11826,7 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
@@ -11559,17 +11834,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS57" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -11707,7 +11987,7 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ58" t="inlineStr">
@@ -11715,17 +11995,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS58" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
@@ -11941,7 +12226,7 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ59" t="inlineStr">
@@ -11949,17 +12234,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS59" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
@@ -12097,7 +12387,7 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ60" t="inlineStr">
@@ -12105,17 +12395,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS60" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -12331,7 +12626,7 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ61" t="inlineStr">
@@ -12339,17 +12634,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS61" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -12487,7 +12787,7 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
@@ -12495,17 +12795,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS62" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -12721,7 +13026,7 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
@@ -12729,17 +13034,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS63" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
@@ -12877,7 +13187,7 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
@@ -12885,17 +13195,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS64" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
@@ -13111,7 +13426,7 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
@@ -13119,17 +13434,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS65" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -13267,7 +13587,7 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ66" t="inlineStr">
@@ -13275,17 +13595,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS66" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -13501,7 +13826,7 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
@@ -13509,17 +13834,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS67" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -13657,7 +13987,7 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ68" t="inlineStr">
@@ -13665,17 +13995,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS68" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -13891,7 +14226,7 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
@@ -13899,17 +14234,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS69" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -14047,7 +14387,7 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
@@ -14055,17 +14395,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS70" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -14281,7 +14626,7 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ71" t="inlineStr">
@@ -14289,17 +14634,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS71" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
@@ -14437,7 +14787,7 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
@@ -14445,17 +14795,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS72" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
@@ -14671,7 +15026,7 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ73" t="inlineStr">
@@ -14679,17 +15034,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS73" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
@@ -14761,12 +15121,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -14800,10 +15160,10 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>1</v>
+        <v>251</v>
       </c>
       <c r="O74" t="n">
-        <v>1</v>
+        <v>251</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -14812,12 +15172,12 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D69_ANNUAL</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -14837,7 +15197,7 @@
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D69_ANNUAL</t>
         </is>
       </c>
       <c r="AT74" t="n">
@@ -14850,42 +15210,42 @@
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -14917,12 +15277,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -14956,24 +15316,24 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>1</v>
+        <v>251</v>
       </c>
       <c r="O75" t="n">
-        <v>1</v>
+        <v>251</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D69_ANNUAL</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D69_ANNUAL</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
@@ -14988,12 +15348,12 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
@@ -15003,7 +15363,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD75" t="inlineStr">
@@ -15038,17 +15398,17 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15071,7 +15431,7 @@
       </c>
       <c r="AS75" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D69_ANNUAL</t>
         </is>
       </c>
       <c r="AT75" t="n">
@@ -15084,42 +15444,42 @@
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -15181,19 +15541,19 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>1983-02-01</t>
+          <t>1983-01-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>1983-02</t>
+          <t>1983-01</t>
         </is>
       </c>
       <c r="N76" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O76" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15217,7 +15577,7 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ76" t="inlineStr">
@@ -15225,17 +15585,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS76" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
@@ -15337,19 +15702,19 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>1983-02-01</t>
+          <t>1983-01-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>1983-02</t>
+          <t>1983-01</t>
         </is>
       </c>
       <c r="N77" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -15451,7 +15816,7 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
@@ -15459,17 +15824,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS77" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
@@ -15571,19 +15941,19 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>1983-03-01</t>
+          <t>1983-02-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>1983-03</t>
+          <t>1983-02</t>
         </is>
       </c>
       <c r="N78" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O78" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -15607,7 +15977,7 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
@@ -15615,17 +15985,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS78" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
@@ -15727,19 +16102,19 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>1983-03-01</t>
+          <t>1983-02-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>1983-03</t>
+          <t>1983-02</t>
         </is>
       </c>
       <c r="N79" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O79" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
@@ -15841,7 +16216,7 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ79" t="inlineStr">
@@ -15849,17 +16224,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS79" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
@@ -15961,19 +16341,19 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>1983-04-01</t>
+          <t>1983-03-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>1983-04</t>
+          <t>1983-03</t>
         </is>
       </c>
       <c r="N80" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O80" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -15997,7 +16377,7 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ80" t="inlineStr">
@@ -16005,17 +16385,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS80" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
@@ -16117,19 +16502,19 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>1983-04-01</t>
+          <t>1983-03-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>1983-04</t>
+          <t>1983-03</t>
         </is>
       </c>
       <c r="N81" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O81" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
@@ -16231,7 +16616,7 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ81" t="inlineStr">
@@ -16239,17 +16624,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS81" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
@@ -16351,61 +16741,66 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>1983-05-01</t>
+          <t>1983-04-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>1983-05</t>
+          <t>1983-04</t>
         </is>
       </c>
       <c r="N82" t="n">
+        <v>7</v>
+      </c>
+      <c r="O82" t="n">
+        <v>7</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT82" t="n">
         <v>2</v>
       </c>
-      <c r="O82" t="n">
-        <v>2</v>
-      </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP82" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ82" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS82" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT82" t="n">
-        <v>1</v>
-      </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
@@ -16507,19 +16902,19 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>1983-05-01</t>
+          <t>1983-04-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>1983-05</t>
+          <t>1983-04</t>
         </is>
       </c>
       <c r="N83" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O83" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U83" t="inlineStr">
         <is>
@@ -16621,7 +17016,7 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ83" t="inlineStr">
@@ -16629,17 +17024,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS83" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
@@ -16741,19 +17141,19 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>1983-06-01</t>
+          <t>1983-05-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>1983-06</t>
+          <t>1983-05</t>
         </is>
       </c>
       <c r="N84" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O84" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -16777,7 +17177,7 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ84" t="inlineStr">
@@ -16785,17 +17185,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS84" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
@@ -16897,19 +17302,19 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>1983-06-01</t>
+          <t>1983-05-01</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>1983-06</t>
+          <t>1983-05</t>
         </is>
       </c>
       <c r="N85" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O85" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U85" t="inlineStr">
         <is>
@@ -17011,7 +17416,7 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ85" t="inlineStr">
@@ -17019,17 +17424,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS85" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
@@ -17131,19 +17541,19 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>1983-07-01</t>
+          <t>1983-06-01</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>1983-07</t>
+          <t>1983-06</t>
         </is>
       </c>
       <c r="N86" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="O86" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -17167,7 +17577,7 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ86" t="inlineStr">
@@ -17175,17 +17585,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS86" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
@@ -17287,19 +17702,19 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>1983-07-01</t>
+          <t>1983-06-01</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>1983-07</t>
+          <t>1983-06</t>
         </is>
       </c>
       <c r="N87" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="O87" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
@@ -17401,7 +17816,7 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ87" t="inlineStr">
@@ -17409,17 +17824,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS87" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
@@ -17521,19 +17941,19 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>1983-08-01</t>
+          <t>1983-07-01</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>1983-08</t>
+          <t>1983-07</t>
         </is>
       </c>
       <c r="N88" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O88" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -17557,7 +17977,7 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ88" t="inlineStr">
@@ -17565,17 +17985,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS88" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
@@ -17677,19 +18102,19 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>1983-08-01</t>
+          <t>1983-07-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>1983-08</t>
+          <t>1983-07</t>
         </is>
       </c>
       <c r="N89" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O89" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -17791,7 +18216,7 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ89" t="inlineStr">
@@ -17799,17 +18224,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS89" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
@@ -17911,19 +18341,19 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>1983-09-01</t>
+          <t>1983-08-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>1983-09</t>
+          <t>1983-08</t>
         </is>
       </c>
       <c r="N90" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O90" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -17947,7 +18377,7 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ90" t="inlineStr">
@@ -17955,17 +18385,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS90" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
@@ -18067,19 +18502,19 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>1983-09-01</t>
+          <t>1983-08-01</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>1983-09</t>
+          <t>1983-08</t>
         </is>
       </c>
       <c r="N91" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O91" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
@@ -18181,7 +18616,7 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ91" t="inlineStr">
@@ -18189,17 +18624,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS91" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
@@ -18301,19 +18741,19 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>1983-10-01</t>
+          <t>1983-09-01</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>1983-10</t>
+          <t>1983-09</t>
         </is>
       </c>
       <c r="N92" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O92" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -18337,7 +18777,7 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ92" t="inlineStr">
@@ -18345,17 +18785,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS92" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
@@ -18457,19 +18902,19 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>1983-10-01</t>
+          <t>1983-09-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>1983-10</t>
+          <t>1983-09</t>
         </is>
       </c>
       <c r="N93" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O93" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
@@ -18571,7 +19016,7 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ93" t="inlineStr">
@@ -18579,17 +19024,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS93" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
@@ -18691,19 +19141,19 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>1983-11-01</t>
+          <t>1983-10-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>1983-11</t>
+          <t>1983-10</t>
         </is>
       </c>
       <c r="N94" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O94" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -18727,7 +19177,7 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ94" t="inlineStr">
@@ -18735,17 +19185,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS94" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
@@ -18847,19 +19302,19 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>1983-11-01</t>
+          <t>1983-10-01</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>1983-11</t>
+          <t>1983-10</t>
         </is>
       </c>
       <c r="N95" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O95" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
@@ -18961,7 +19416,7 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ95" t="inlineStr">
@@ -18969,17 +19424,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS95" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
@@ -19081,61 +19541,66 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>1983-12-01</t>
+          <t>1983-11-01</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>1983-12</t>
+          <t>1983-11</t>
         </is>
       </c>
       <c r="N96" t="n">
+        <v>6</v>
+      </c>
+      <c r="O96" t="n">
+        <v>6</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP96" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ96" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT96" t="n">
         <v>2</v>
       </c>
-      <c r="O96" t="n">
-        <v>2</v>
-      </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP96" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ96" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS96" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT96" t="n">
-        <v>1</v>
-      </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
@@ -19237,19 +19702,19 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>1983-12-01</t>
+          <t>1983-11-01</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>1983-12</t>
+          <t>1983-11</t>
         </is>
       </c>
       <c r="N97" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O97" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -19351,7 +19816,7 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
@@ -19359,17 +19824,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS97" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
@@ -19471,19 +19941,19 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>1984-01-01</t>
+          <t>1983-12-01</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>1984-01</t>
+          <t>1983-12</t>
         </is>
       </c>
       <c r="N98" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O98" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -19507,7 +19977,7 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ98" t="inlineStr">
@@ -19515,17 +19985,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS98" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
@@ -19627,19 +20102,19 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>1984-01-01</t>
+          <t>1983-12-01</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>1984-01</t>
+          <t>1983-12</t>
         </is>
       </c>
       <c r="N99" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O99" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
@@ -19741,7 +20216,7 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ99" t="inlineStr">
@@ -19749,17 +20224,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS99" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
@@ -19831,12 +20311,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -19861,19 +20341,19 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>1984-02-01</t>
+          <t>1984-01-01</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>1984-02</t>
+          <t>1984-01</t>
         </is>
       </c>
       <c r="N100" t="n">
-        <v>5</v>
+        <v>293</v>
       </c>
       <c r="O100" t="n">
-        <v>5</v>
+        <v>293</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -19882,12 +20362,12 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D69_ANNUAL</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -19907,7 +20387,7 @@
       </c>
       <c r="AS100" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D69_ANNUAL</t>
         </is>
       </c>
       <c r="AT100" t="n">
@@ -19920,42 +20400,42 @@
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19987,12 +20467,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -20017,33 +20497,33 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>1984-02-01</t>
+          <t>1984-01-01</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>1984-02</t>
+          <t>1984-01</t>
         </is>
       </c>
       <c r="N101" t="n">
-        <v>5</v>
+        <v>293</v>
       </c>
       <c r="O101" t="n">
-        <v>5</v>
+        <v>293</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D69_ANNUAL</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D69_ANNUAL</t>
         </is>
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X101" t="inlineStr">
@@ -20058,12 +20538,12 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
@@ -20073,7 +20553,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD101" t="inlineStr">
@@ -20108,17 +20588,17 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -20141,7 +20621,7 @@
       </c>
       <c r="AS101" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D69_ANNUAL</t>
         </is>
       </c>
       <c r="AT101" t="n">
@@ -20154,42 +20634,42 @@
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20251,61 +20731,66 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>1984-03-01</t>
+          <t>1984-01-01</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>1984-03</t>
+          <t>1984-01</t>
         </is>
       </c>
       <c r="N102" t="n">
+        <v>4</v>
+      </c>
+      <c r="O102" t="n">
+        <v>4</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ102" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT102" t="n">
         <v>2</v>
       </c>
-      <c r="O102" t="n">
-        <v>2</v>
-      </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U102" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA102" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP102" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ102" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS102" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT102" t="n">
-        <v>1</v>
-      </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
@@ -20407,19 +20892,19 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>1984-03-01</t>
+          <t>1984-01-01</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>1984-03</t>
+          <t>1984-01</t>
         </is>
       </c>
       <c r="N103" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O103" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
@@ -20521,7 +21006,7 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ103" t="inlineStr">
@@ -20529,17 +21014,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS103" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
@@ -20641,19 +21131,19 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>1984-04-01</t>
+          <t>1984-02-01</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>1984-04</t>
+          <t>1984-02</t>
         </is>
       </c>
       <c r="N104" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O104" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -20677,7 +21167,7 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
@@ -20685,17 +21175,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS104" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
@@ -20797,19 +21292,19 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>1984-04-01</t>
+          <t>1984-02-01</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>1984-04</t>
+          <t>1984-02</t>
         </is>
       </c>
       <c r="N105" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O105" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
@@ -20911,7 +21406,7 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
@@ -20919,17 +21414,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS105" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
@@ -21031,19 +21531,19 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>1984-05-01</t>
+          <t>1984-03-01</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>1984-05</t>
+          <t>1984-03</t>
         </is>
       </c>
       <c r="N106" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O106" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -21067,7 +21567,7 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
@@ -21075,17 +21575,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS106" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
@@ -21187,19 +21692,19 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>1984-05-01</t>
+          <t>1984-03-01</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>1984-05</t>
+          <t>1984-03</t>
         </is>
       </c>
       <c r="N107" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O107" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U107" t="inlineStr">
         <is>
@@ -21301,7 +21806,7 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
@@ -21309,17 +21814,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS107" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
@@ -21421,19 +21931,19 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>1984-06-01</t>
+          <t>1984-04-01</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>1984-06</t>
+          <t>1984-04</t>
         </is>
       </c>
       <c r="N108" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O108" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -21457,7 +21967,7 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ108" t="inlineStr">
@@ -21465,17 +21975,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS108" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
@@ -21577,19 +22092,19 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>1984-06-01</t>
+          <t>1984-04-01</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>1984-06</t>
+          <t>1984-04</t>
         </is>
       </c>
       <c r="N109" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O109" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
@@ -21691,7 +22206,7 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ109" t="inlineStr">
@@ -21699,17 +22214,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS109" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
@@ -21811,19 +22331,19 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>1984-07-01</t>
+          <t>1984-05-01</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>1984-07</t>
+          <t>1984-05</t>
         </is>
       </c>
       <c r="N110" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O110" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -21847,7 +22367,7 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ110" t="inlineStr">
@@ -21855,17 +22375,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS110" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
@@ -21967,19 +22492,19 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>1984-07-01</t>
+          <t>1984-05-01</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>1984-07</t>
+          <t>1984-05</t>
         </is>
       </c>
       <c r="N111" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O111" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="U111" t="inlineStr">
         <is>
@@ -22081,7 +22606,7 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ111" t="inlineStr">
@@ -22089,17 +22614,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS111" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
@@ -22201,19 +22731,19 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>1984-08-01</t>
+          <t>1984-06-01</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>1984-08</t>
+          <t>1984-06</t>
         </is>
       </c>
       <c r="N112" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O112" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -22237,7 +22767,7 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ112" t="inlineStr">
@@ -22245,17 +22775,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS112" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
@@ -22357,19 +22892,19 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>1984-08-01</t>
+          <t>1984-06-01</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>1984-08</t>
+          <t>1984-06</t>
         </is>
       </c>
       <c r="N113" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O113" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="U113" t="inlineStr">
         <is>
@@ -22471,7 +23006,7 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ113" t="inlineStr">
@@ -22479,17 +23014,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS113" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
@@ -22591,19 +23131,19 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>1984-09-01</t>
+          <t>1984-07-01</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>1984-09</t>
+          <t>1984-07</t>
         </is>
       </c>
       <c r="N114" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O114" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -22627,7 +23167,7 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ114" t="inlineStr">
@@ -22635,17 +23175,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS114" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
@@ -22747,19 +23292,19 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>1984-09-01</t>
+          <t>1984-07-01</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>1984-09</t>
+          <t>1984-07</t>
         </is>
       </c>
       <c r="N115" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O115" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U115" t="inlineStr">
         <is>
@@ -22861,7 +23406,7 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ115" t="inlineStr">
@@ -22869,17 +23414,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS115" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
@@ -22981,19 +23531,19 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>1984-10-01</t>
+          <t>1984-08-01</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>1984-10</t>
+          <t>1984-08</t>
         </is>
       </c>
       <c r="N116" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O116" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -23017,7 +23567,7 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ116" t="inlineStr">
@@ -23025,17 +23575,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS116" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
@@ -23137,19 +23692,19 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>1984-10-01</t>
+          <t>1984-08-01</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>1984-10</t>
+          <t>1984-08</t>
         </is>
       </c>
       <c r="N117" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O117" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="U117" t="inlineStr">
         <is>
@@ -23251,7 +23806,7 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ117" t="inlineStr">
@@ -23259,17 +23814,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS117" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
@@ -23371,19 +23931,19 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>1984-11-01</t>
+          <t>1984-09-01</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>1984-11</t>
+          <t>1984-09</t>
         </is>
       </c>
       <c r="N118" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O118" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -23407,7 +23967,7 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ118" t="inlineStr">
@@ -23415,17 +23975,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS118" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
@@ -23527,19 +24092,19 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>1984-11-01</t>
+          <t>1984-09-01</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>1984-11</t>
+          <t>1984-09</t>
         </is>
       </c>
       <c r="N119" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O119" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
@@ -23641,7 +24206,7 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ119" t="inlineStr">
@@ -23649,17 +24214,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS119" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
@@ -23761,19 +24331,19 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>1984-12-01</t>
+          <t>1984-10-01</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>1984-12</t>
+          <t>1984-10</t>
         </is>
       </c>
       <c r="N120" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O120" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -23797,7 +24367,7 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ120" t="inlineStr">
@@ -23805,17 +24375,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS120" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
@@ -23917,19 +24492,19 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>1984-12-01</t>
+          <t>1984-10-01</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>1984-12</t>
+          <t>1984-10</t>
         </is>
       </c>
       <c r="N121" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O121" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
@@ -24031,7 +24606,7 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ121" t="inlineStr">
@@ -24039,55 +24614,860 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS121" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV121" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA121" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB121" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC121" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>1984-11-01</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>1984-11</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>7</v>
+      </c>
+      <c r="O122" t="n">
+        <v>7</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>1984-11-01</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>1984-11</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>7</v>
+      </c>
+      <c r="O123" t="n">
+        <v>7</v>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN123" t="b">
         <v>1</v>
       </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV121" t="inlineStr">
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV123" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW121" t="inlineStr">
+      <c r="AW123" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX121" t="inlineStr">
+      <c r="AX123" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY121" t="inlineStr">
+      <c r="AY123" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ121" t="inlineStr">
+      <c r="AZ123" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA121" t="inlineStr">
+      <c r="BA123" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB121" t="inlineStr">
+      <c r="BB123" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC121" t="inlineStr">
+      <c r="BC123" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>1984-12-01</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>1984-12</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>3</v>
+      </c>
+      <c r="O124" t="n">
+        <v>3</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>1984-12-01</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>1984-12</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>3</v>
+      </c>
+      <c r="O125" t="n">
+        <v>3</v>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN125" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT125" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -24209,7 +25589,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
@@ -24219,7 +25599,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11">
@@ -24239,7 +25619,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -24249,7 +25629,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -24271,7 +25651,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>235</v>
+        <v>779</v>
       </c>
     </row>
     <row r="16">
